--- a/data/trans_orig/P19C04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>51546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41524</t>
+          <t>41671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54992</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>87452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>139947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>163053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159698</t>
+          <t>159551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181123</t>
+          <t>179543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>307516</t>
+          <t>305264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337724</t>
+          <t>336029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78252</t>
+          <t>81692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114191</t>
+          <t>115983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70191</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105360</t>
+          <t>105180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159621</t>
+          <t>161421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207383</t>
+          <t>207568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295565</t>
+          <t>293773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331504</t>
+          <t>328064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335841</t>
+          <t>336021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371010</t>
+          <t>369869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643574</t>
+          <t>643389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691336</t>
+          <t>689536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38613</t>
+          <t>38283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>49411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70436</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104511</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172680</t>
+          <t>174029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197924</t>
+          <t>198254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241481</t>
+          <t>239395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262871</t>
+          <t>262455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420832</t>
+          <t>418282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454907</t>
+          <t>454824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62480</t>
+          <t>62811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>94678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210186</t>
+          <t>211543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235185</t>
+          <t>235625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>252023</t>
+          <t>252336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274313</t>
+          <t>274552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474247</t>
+          <t>472387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>504585</t>
+          <t>504254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76455</t>
+          <t>78233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121896</t>
+          <t>121992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>142848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134515</t>
+          <t>137076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156458</t>
+          <t>157604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267729</t>
+          <t>265951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295495</t>
+          <t>296003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65384</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148048</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169379</t>
+          <t>168836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174181</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191244</t>
+          <t>191664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328374</t>
+          <t>328454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355381</t>
+          <t>355097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>73776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109008</t>
+          <t>108996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>64939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101666</t>
+          <t>99203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150217</t>
+          <t>148818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198383</t>
+          <t>197939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>355317</t>
+          <t>355329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>389124</t>
+          <t>390549</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>437702</t>
+          <t>440165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>472146</t>
+          <t>474429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>805309</t>
+          <t>805753</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>853475</t>
+          <t>854874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87156</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124422</t>
+          <t>122785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68405</t>
+          <t>69700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>104861</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166405</t>
+          <t>165256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215281</t>
+          <t>218355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>401130</t>
+          <t>402767</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>438396</t>
+          <t>437823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>488871</t>
+          <t>487551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>524007</t>
+          <t>522712</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>902682</t>
+          <t>899608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>951558</t>
+          <t>952707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>450878</t>
+          <t>449175</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>531386</t>
+          <t>530224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>364094</t>
+          <t>368865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>437561</t>
+          <t>439813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>834415</t>
+          <t>838333</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>948895</t>
+          <t>946159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1923356</t>
+          <t>1924518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2003864</t>
+          <t>2005567</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2303376</t>
+          <t>2301124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2376843</t>
+          <t>2372072</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4246784</t>
+          <t>4249520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4361264</t>
+          <t>4357346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>60933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90755</t>
+          <t>90379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64065</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103502</t>
+          <t>105949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142886</t>
+          <t>148281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159805</t>
+          <t>160181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189511</t>
+          <t>189627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185174</t>
+          <t>184853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212849</t>
+          <t>213306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356914</t>
+          <t>351519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>396298</t>
+          <t>393851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95323</t>
+          <t>95454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135206</t>
+          <t>132596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61128</t>
+          <t>63507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94584</t>
+          <t>95878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166396</t>
+          <t>167342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218423</t>
+          <t>220540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271124</t>
+          <t>273734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311007</t>
+          <t>310876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343239</t>
+          <t>341945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376695</t>
+          <t>374316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>625730</t>
+          <t>623613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>677757</t>
+          <t>676811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66348</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97899</t>
+          <t>97587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>54478</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80744</t>
+          <t>82877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127246</t>
+          <t>126701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170234</t>
+          <t>168058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195765</t>
+          <t>196077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227316</t>
+          <t>225914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248008</t>
+          <t>245875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>274274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>452182</t>
+          <t>454358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495170</t>
+          <t>495715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106601</t>
+          <t>105113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49231</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77206</t>
+          <t>78130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129884</t>
+          <t>130324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176694</t>
+          <t>173382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206476</t>
+          <t>207964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>239108</t>
+          <t>240308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265609</t>
+          <t>264685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293584</t>
+          <t>292676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>479197</t>
+          <t>482509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>526007</t>
+          <t>525567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42389</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68400</t>
+          <t>69149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>54915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83014</t>
+          <t>82389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115175</t>
+          <t>116592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123658</t>
+          <t>122909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149669</t>
+          <t>149554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139168</t>
+          <t>140659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>163528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272457</t>
+          <t>271040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304618</t>
+          <t>305243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>66207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96540</t>
+          <t>97039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48608</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>75518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123338</t>
+          <t>124211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166084</t>
+          <t>165103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153433</t>
+          <t>152934</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184459</t>
+          <t>183766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186538</t>
+          <t>189312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216222</t>
+          <t>216509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>348719</t>
+          <t>349700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391465</t>
+          <t>390592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96712</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136542</t>
+          <t>137512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>65266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101571</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173701</t>
+          <t>174886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226106</t>
+          <t>228519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>438549</t>
+          <t>437579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>478379</t>
+          <t>479191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>523388</t>
+          <t>522336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>559346</t>
+          <t>559693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>973944</t>
+          <t>971531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1026349</t>
+          <t>1025164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87775</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127571</t>
+          <t>127723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89500</t>
+          <t>89977</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127787</t>
+          <t>129086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186784</t>
+          <t>186647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242594</t>
+          <t>240891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>506182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>546130</t>
+          <t>545345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>573443</t>
+          <t>572144</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>611730</t>
+          <t>611253</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1092541</t>
+          <t>1094244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1148351</t>
+          <t>1148488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>672392</t>
+          <t>676315</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>772075</t>
+          <t>774731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>509695</t>
+          <t>507321</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>593783</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1210693</t>
+          <t>1204086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1340636</t>
+          <t>1338789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2142584</t>
+          <t>2139928</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2242267</t>
+          <t>2238344</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2551438</t>
+          <t>2552889</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2635526</t>
+          <t>2637900</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4719243</t>
+          <t>4721090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4849186</t>
+          <t>4855793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35990</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63334</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68469</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103270</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181884</t>
+          <t>180551</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209228</t>
+          <t>206865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197923</t>
+          <t>198384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221283</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387187</t>
+          <t>387306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>421988</t>
+          <t>421222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52863</t>
+          <t>52535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63282</t>
+          <t>65739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97844</t>
+          <t>99274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138812</t>
+          <t>140851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280569</t>
+          <t>281620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310302</t>
+          <t>310630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330045</t>
+          <t>327588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356504</t>
+          <t>355207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617680</t>
+          <t>615641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>658648</t>
+          <t>657218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44475</t>
+          <t>44172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72620</t>
+          <t>72500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247857</t>
+          <t>245502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268015</t>
+          <t>267256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271033</t>
+          <t>270650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290317</t>
+          <t>289458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525650</t>
+          <t>525770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>553795</t>
+          <t>554098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61466</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92196</t>
+          <t>91018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61415</t>
+          <t>61168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100031</t>
+          <t>103436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141954</t>
+          <t>143442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237851</t>
+          <t>239029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268581</t>
+          <t>269317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287446</t>
+          <t>287693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314867</t>
+          <t>314268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>536954</t>
+          <t>535466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578877</t>
+          <t>575472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33828</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56435</t>
+          <t>55609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106685</t>
+          <t>106469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>111847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130614</t>
+          <t>130645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208287</t>
+          <t>209113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231442</t>
+          <t>232712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81819</t>
+          <t>80296</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96524</t>
+          <t>97205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134366</t>
+          <t>137327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151796</t>
+          <t>153319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179000</t>
+          <t>182117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183147</t>
+          <t>183793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208312</t>
+          <t>209417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346387</t>
+          <t>343426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384229</t>
+          <t>383548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45510</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>76358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65751</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>91281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>365596</t>
+          <t>365949</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396797</t>
+          <t>396781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>421300</t>
+          <t>420499</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>448884</t>
+          <t>449868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>795921</t>
+          <t>796950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>837901</t>
+          <t>838077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>88420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124890</t>
+          <t>123886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112067</t>
+          <t>112808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171718</t>
+          <t>170670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224725</t>
+          <t>224448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>515362</t>
+          <t>516366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>552771</t>
+          <t>551832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579274</t>
+          <t>578533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>616131</t>
+          <t>614690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1106868</t>
+          <t>1107145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1159875</t>
+          <t>1160923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>436630</t>
+          <t>437264</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518235</t>
+          <t>516550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>373344</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>333507</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>410704</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>849072</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>796671</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>906223</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>373344</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>335473</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>413296</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>849072</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>794359</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>903583</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2146098</t>
+          <t>2147783</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2227703</t>
+          <t>2227069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,82 +10251,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2492877</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2455517</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2532714</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4681482</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>4624331</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4733883</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>84,65%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>83,61%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2381</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2492877</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>2452925</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2530748</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4681482</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>4626971</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4736195</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>83,66%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54375</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57452</t>
+          <t>57861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86827</t>
+          <t>86588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251055</t>
+          <t>250792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276504</t>
+          <t>275154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248441</t>
+          <t>247844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264306</t>
+          <t>264041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506210</t>
+          <t>506449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535585</t>
+          <t>535176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27178</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59129</t>
+          <t>61556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>32255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51516</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62312</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447855</t>
+          <t>445428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479806</t>
+          <t>480644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450032</t>
+          <t>448552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470351</t>
+          <t>469293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908368</t>
+          <t>906958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>946220</t>
+          <t>944588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>66572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42997</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63932</t>
+          <t>63925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93391</t>
+          <t>92929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123239</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232229</t>
+          <t>234620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257440</t>
+          <t>258139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271343</t>
+          <t>271350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>292278</t>
+          <t>293450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>513228</t>
+          <t>511661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543076</t>
+          <t>543538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>52521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61563</t>
+          <t>64331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112202</t>
+          <t>111353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>275091</t>
+          <t>274167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422070</t>
+          <t>420944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450873</t>
+          <t>448800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671383</t>
+          <t>672232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722022</t>
+          <t>719254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44877</t>
+          <t>44163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33167</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52358</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72654</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123552</t>
+          <t>124266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140255</t>
+          <t>140617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169125</t>
+          <t>169201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>180760</t>
+          <t>181660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298067</t>
+          <t>298450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318363</t>
+          <t>319338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>61183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40659</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85980</t>
+          <t>86292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113565</t>
+          <t>112413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192669</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>212638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188212</t>
+          <t>188277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205691</t>
+          <t>205376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>386517</t>
+          <t>387669</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414102</t>
+          <t>413790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55231</t>
+          <t>57575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94701</t>
+          <t>93712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80179</t>
+          <t>82405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163943</t>
+          <t>164790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>504994</t>
+          <t>505983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>544464</t>
+          <t>542120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>743465</t>
+          <t>746340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801320</t>
+          <t>803020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1264117</t>
+          <t>1263270</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347881</t>
+          <t>1345655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58852</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202711</t>
+          <t>201075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67275</t>
+          <t>67629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95637</t>
+          <t>94783</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118247</t>
+          <t>135846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269668</t>
+          <t>271269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>704831</t>
+          <t>706467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>848690</t>
+          <t>848261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>608287</t>
+          <t>609141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636649</t>
+          <t>636295</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1341799</t>
+          <t>1340198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1493220</t>
+          <t>1475621</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>374856</t>
+          <t>376258</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>544619</t>
+          <t>540180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>308764</t>
+          <t>305337</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>417583</t>
+          <t>415367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>745530</t>
+          <t>757706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>940970</t>
+          <t>944760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2808506</t>
+          <t>2812945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2978269</t>
+          <t>2976867</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3161244</t>
+          <t>3163460</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3270063</t>
+          <t>3273490</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5990982</t>
+          <t>5987192</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6186422</t>
+          <t>6174246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28440</t>
+          <t>28705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51546</t>
+          <t>51260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56687</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87452</t>
+          <t>85643</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>140233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163053</t>
+          <t>162788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159551</t>
+          <t>159413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179543</t>
+          <t>179505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305264</t>
+          <t>307073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>336029</t>
+          <t>336208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81692</t>
+          <t>81736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115983</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>70970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105180</t>
+          <t>102794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161421</t>
+          <t>160210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207568</t>
+          <t>210200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293773</t>
+          <t>293205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328064</t>
+          <t>328020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336021</t>
+          <t>338407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369869</t>
+          <t>370231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643389</t>
+          <t>640757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689536</t>
+          <t>690747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49411</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70519</t>
+          <t>70057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107061</t>
+          <t>102691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174029</t>
+          <t>171656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198254</t>
+          <t>197661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239395</t>
+          <t>241485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262455</t>
+          <t>263026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>418282</t>
+          <t>422652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454824</t>
+          <t>455286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>46641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62811</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94678</t>
+          <t>93449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211543</t>
+          <t>213705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235625</t>
+          <t>235612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>252336</t>
+          <t>252893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274552</t>
+          <t>274523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>472387</t>
+          <t>473616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>504254</t>
+          <t>503854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48181</t>
+          <t>49268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78233</t>
+          <t>78316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121992</t>
+          <t>122635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142848</t>
+          <t>142942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137076</t>
+          <t>136075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157604</t>
+          <t>156731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265951</t>
+          <t>265868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296003</t>
+          <t>294916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>65055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148794</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168836</t>
+          <t>168632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174306</t>
+          <t>173982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191664</t>
+          <t>190635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328454</t>
+          <t>328703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355097</t>
+          <t>354743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73776</t>
+          <t>74636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108996</t>
+          <t>109355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64939</t>
+          <t>67227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>99491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148818</t>
+          <t>147891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197939</t>
+          <t>194917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>355329</t>
+          <t>354970</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>390549</t>
+          <t>389689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>440165</t>
+          <t>439877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>474429</t>
+          <t>472141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>805753</t>
+          <t>808775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>854874</t>
+          <t>855801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87729</t>
+          <t>86650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122785</t>
+          <t>122924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69700</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104861</t>
+          <t>102794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>165256</t>
+          <t>167240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218355</t>
+          <t>213980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>402767</t>
+          <t>402628</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>437823</t>
+          <t>438902</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>487551</t>
+          <t>489618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>522712</t>
+          <t>524891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>899608</t>
+          <t>903983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>952707</t>
+          <t>950723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>449175</t>
+          <t>452315</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>530224</t>
+          <t>532460</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>368865</t>
+          <t>368079</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>439813</t>
+          <t>443924</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>838333</t>
+          <t>838459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>946159</t>
+          <t>950149</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1924518</t>
+          <t>1922282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2005567</t>
+          <t>2002427</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2301124</t>
+          <t>2297013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2372072</t>
+          <t>2372858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4249520</t>
+          <t>4245530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4357346</t>
+          <t>4357220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90379</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>37036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64386</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>107689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148281</t>
+          <t>145540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160181</t>
+          <t>160116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189627</t>
+          <t>190472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>184853</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213306</t>
+          <t>212203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>351519</t>
+          <t>354260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393851</t>
+          <t>392111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95454</t>
+          <t>96565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132596</t>
+          <t>133304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63507</t>
+          <t>63857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95878</t>
+          <t>94087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167342</t>
+          <t>168607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220540</t>
+          <t>217534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273734</t>
+          <t>273026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310876</t>
+          <t>309765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341945</t>
+          <t>343736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374316</t>
+          <t>373966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623613</t>
+          <t>626619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>676811</t>
+          <t>675546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97587</t>
+          <t>98031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>81528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126701</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>169026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196077</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225914</t>
+          <t>226816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245875</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>274274</t>
+          <t>277294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454358</t>
+          <t>453390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495715</t>
+          <t>496231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72769</t>
+          <t>74395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>107066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78130</t>
+          <t>77509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130324</t>
+          <t>131067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173382</t>
+          <t>176823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207964</t>
+          <t>206011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240308</t>
+          <t>238682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264685</t>
+          <t>265306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>292676</t>
+          <t>295044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482509</t>
+          <t>479068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>525567</t>
+          <t>524824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42504</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69149</t>
+          <t>68711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>32537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54915</t>
+          <t>55649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>81082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116592</t>
+          <t>118125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122909</t>
+          <t>123347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149554</t>
+          <t>149597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140659</t>
+          <t>139925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163528</t>
+          <t>163037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271040</t>
+          <t>269507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305243</t>
+          <t>306550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97039</t>
+          <t>98324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48321</t>
+          <t>48338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>76217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124211</t>
+          <t>122961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165103</t>
+          <t>164334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152934</t>
+          <t>151649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183766</t>
+          <t>183392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189312</t>
+          <t>188613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216509</t>
+          <t>216492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349700</t>
+          <t>350469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>390592</t>
+          <t>391842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95900</t>
+          <t>98117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>139025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65266</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102623</t>
+          <t>103852</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174886</t>
+          <t>174198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>227038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>437579</t>
+          <t>436066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>479191</t>
+          <t>476974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>522336</t>
+          <t>521107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>559693</t>
+          <t>559072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>971531</t>
+          <t>973012</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1025164</t>
+          <t>1025852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>88625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127723</t>
+          <t>127783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89977</t>
+          <t>90493</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129086</t>
+          <t>130476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186647</t>
+          <t>188088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240891</t>
+          <t>245221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>506182</t>
+          <t>506122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>545345</t>
+          <t>545280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>572144</t>
+          <t>570754</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>611253</t>
+          <t>610737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1094244</t>
+          <t>1089914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1148488</t>
+          <t>1147047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>676315</t>
+          <t>669120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>774731</t>
+          <t>766749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>507321</t>
+          <t>512065</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>603803</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1204086</t>
+          <t>1206019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1338789</t>
+          <t>1337771</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2139928</t>
+          <t>2147910</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2238344</t>
+          <t>2245539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2552889</t>
+          <t>2541418</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2637900</t>
+          <t>2633156</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4721090</t>
+          <t>4722108</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4855793</t>
+          <t>4853860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38353</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64667</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>46280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69235</t>
+          <t>69783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103151</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>180551</t>
+          <t>179897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206865</t>
+          <t>206910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198384</t>
+          <t>198959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220200</t>
+          <t>221324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387306</t>
+          <t>387227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>421222</t>
+          <t>420674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81545</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65739</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99274</t>
+          <t>99169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140851</t>
+          <t>138299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281620</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310630</t>
+          <t>311711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327588</t>
+          <t>328671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355207</t>
+          <t>355666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615641</t>
+          <t>618193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657218</t>
+          <t>657323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44172</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245502</t>
+          <t>247313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267256</t>
+          <t>267446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270650</t>
+          <t>271827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289458</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525770</t>
+          <t>525780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>554098</t>
+          <t>553401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60730</t>
+          <t>63225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91018</t>
+          <t>94472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61168</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103436</t>
+          <t>101162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143442</t>
+          <t>142830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239029</t>
+          <t>235575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269317</t>
+          <t>266822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287693</t>
+          <t>287647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314268</t>
+          <t>313596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535466</t>
+          <t>536078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>575472</t>
+          <t>577746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55609</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>90918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106469</t>
+          <t>106436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111847</t>
+          <t>112745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130645</t>
+          <t>130629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209113</t>
+          <t>208853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232712</t>
+          <t>232580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>53477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80296</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63344</t>
+          <t>64276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97205</t>
+          <t>97884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137327</t>
+          <t>137028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153319</t>
+          <t>153244</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182117</t>
+          <t>180138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183793</t>
+          <t>182861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209417</t>
+          <t>208491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343426</t>
+          <t>343725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>383548</t>
+          <t>382869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76358</t>
+          <t>75916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66552</t>
+          <t>65182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91281</t>
+          <t>92042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132408</t>
+          <t>131752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>365949</t>
+          <t>366391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396781</t>
+          <t>396296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>420499</t>
+          <t>421869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>449868</t>
+          <t>449187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>796950</t>
+          <t>797606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>838077</t>
+          <t>837316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88420</t>
+          <t>85307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123886</t>
+          <t>123792</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76651</t>
+          <t>74774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112808</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170670</t>
+          <t>172530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224448</t>
+          <t>224252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>516366</t>
+          <t>516460</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>551832</t>
+          <t>554945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>578533</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>614690</t>
+          <t>616567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1107145</t>
+          <t>1107341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1160923</t>
+          <t>1159063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>437264</t>
+          <t>439636</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>516550</t>
+          <t>519767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>333507</t>
+          <t>337268</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>410704</t>
+          <t>413031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>796671</t>
+          <t>790208</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>906223</t>
+          <t>899820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2147783</t>
+          <t>2144566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2227069</t>
+          <t>2224697</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2455517</t>
+          <t>2453190</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2532714</t>
+          <t>2528953</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4624331</t>
+          <t>4630734</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4733883</t>
+          <t>4740346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>78554</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57861</t>
+          <t>64954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86588</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264645</t>
+          <t>254685</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250792</t>
+          <t>242586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275154</t>
+          <t>265756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257489</t>
+          <t>277142</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247844</t>
+          <t>267390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264041</t>
+          <t>284467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>522134</t>
+          <t>531827</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506449</t>
+          <t>515241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535176</t>
+          <t>545427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>39385</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61556</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52996</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63944</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101574</t>
+          <t>101180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>468085</t>
+          <t>478643</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445428</t>
+          <t>460785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480644</t>
+          <t>491799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460555</t>
+          <t>489533</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448552</t>
+          <t>478158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469293</t>
+          <t>498915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>928640</t>
+          <t>968177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906958</t>
+          <t>948460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944588</t>
+          <t>983958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66572</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52908</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63925</t>
+          <t>66982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>107778</t>
+          <t>113312</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92929</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>130625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>246322</t>
+          <t>241776</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234620</t>
+          <t>228265</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258139</t>
+          <t>253007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>282367</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271350</t>
+          <t>274723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293450</t>
+          <t>296480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>528689</t>
+          <t>528623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>511661</t>
+          <t>511310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543538</t>
+          <t>544121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35953</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>83558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>43408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52521</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87587</t>
+          <t>106900</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>88177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111353</t>
+          <t>130526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>260272</t>
+          <t>307246</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244313</t>
+          <t>287180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274167</t>
+          <t>324261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>435726</t>
+          <t>376205</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>420944</t>
+          <t>364243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>448800</t>
+          <t>386084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>695998</t>
+          <t>683451</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672232</t>
+          <t>659825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719254</t>
+          <t>702174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>42500</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27812</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>29975</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33091</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61904</t>
+          <t>72475</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>84490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>132966</t>
+          <t>146799</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124266</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140617</t>
+          <t>156085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>175851</t>
+          <t>189827</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169201</t>
+          <t>181334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181660</t>
+          <t>195873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>308817</t>
+          <t>336626</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298450</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319338</t>
+          <t>347549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>50439</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61183</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>61213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>99185</t>
+          <t>101236</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86292</t>
+          <t>88088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112413</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>203447</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>188047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212638</t>
+          <t>208748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>197450</t>
+          <t>200763</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188277</t>
+          <t>190347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205376</t>
+          <t>208996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>400897</t>
+          <t>400058</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>387669</t>
+          <t>386092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413790</t>
+          <t>413206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>73411</t>
+          <t>86540</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>67075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93712</t>
+          <t>106651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>68192</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>55578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>82858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>154732</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82405</t>
+          <t>132551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164790</t>
+          <t>179911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526284</t>
+          <t>611140</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505983</t>
+          <t>591029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>542120</t>
+          <t>630605</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>769502</t>
+          <t>673194</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>746340</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>803020</t>
+          <t>685808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1295786</t>
+          <t>1284334</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1263270</t>
+          <t>1259155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1345655</t>
+          <t>1306515</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>141416</t>
+          <t>168874</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59281</t>
+          <t>144052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>80439</t>
+          <t>95486</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>80299</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94783</t>
+          <t>112561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>221855</t>
+          <t>264360</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135846</t>
+          <t>236188</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271269</t>
+          <t>293632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>766126</t>
+          <t>600977</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>706467</t>
+          <t>578303</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>848261</t>
+          <t>625799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>623485</t>
+          <t>714821</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>609141</t>
+          <t>697746</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636295</t>
+          <t>730008</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1389612</t>
+          <t>1315798</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1340198</t>
+          <t>1286526</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1475621</t>
+          <t>1343970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>376258</t>
+          <t>503648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>540180</t>
+          <t>599034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>305337</t>
+          <t>388067</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>415367</t>
+          <t>448988</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>757706</t>
+          <t>916155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>944760</t>
+          <t>1027041</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2868148</t>
+          <t>2840562</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2812945</t>
+          <t>2797445</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2976867</t>
+          <t>2892831</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3202425</t>
+          <t>3208332</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3163460</t>
+          <t>3176460</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3273490</t>
+          <t>3237381</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6070573</t>
+          <t>6048894</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5987192</t>
+          <t>5994885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6174246</t>
+          <t>6105771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
